--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44468</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45477</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45541</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45548</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45891</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45790</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45575</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45541</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45400</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45026</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45950</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45385</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45399</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44822</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45466</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44641</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45420</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>44468</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45961</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>45982</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45147</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45399</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>46269</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>46280</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45629</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45723</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>44490</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45690</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45702</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45723</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44876</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46041</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>45259</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>44917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>46083</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44893</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>46274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45132</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45016</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>45595</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44811</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45512</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>45624</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45324</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45328</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45324</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45714</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45566</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>46142</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44705</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45695</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45971</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45450</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45982</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>45239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45352</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45755</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45901</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>46050</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>46078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>46185</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>46195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44526</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44876</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44732</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45273</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>45690</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45225</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45393</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45635</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45628</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44942</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44683</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>45478</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45477</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45755</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45839</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46171</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>46273</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44609</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44564</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>44477</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44827</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44833</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>44520</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>44564</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44608</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>44676</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44480</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>44712</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44809</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>44831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44532</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>44536</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>44839</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44468</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44482</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44673</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44705</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44831</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44831</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44488</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44833</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>44594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44594</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44831</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>44526</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44462</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44811</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44827</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44490</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44683</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44482</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44743</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>44755</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>44593</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44496</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44519</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44519</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44520</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44473</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44532</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44532</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44713</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44741</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44552</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44686</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>44825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44526</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>44643</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44612</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44794</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44531</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44484</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44712</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44645</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44794</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45736</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45477</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45063</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44609</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44868</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45363</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>44958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45695</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45695</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44651</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>45127</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45352</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45008</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>44992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45610</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45610</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44960</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>44963</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45537</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45355</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44992</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45685</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45566</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44473</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45335</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45748</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>44896</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45573</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45310</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45180</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45191</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45194</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>45637</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44903</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45184</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45370</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44981</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45399</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45730</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>44949</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45376</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44519</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45335</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44473</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45432</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45414</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>44935</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45677</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45271</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44894</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45693</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45719</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45439</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45467</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44827</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45568</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44970</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45455</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45681</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44827</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45616</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45735</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45155</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45477</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45146</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45341</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44593</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45218</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45412</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45615</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44975</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45723</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45086</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45070</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45723</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45713</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44484</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45175</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45047</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44781</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45714</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44818</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45047</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45216</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45635</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45755</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45079</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45488</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44526</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45723</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45390</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44824</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>44496</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>44749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44826</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45481</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45360</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45442</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45209</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45582</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46008</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45755</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45505</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45218</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45783</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45884</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45372</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>44547</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45160</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>44939</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>46051</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45827</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45121</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45152</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45918</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45168</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>46008</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44882</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45842</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45197</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44819</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45939</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45252</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44991</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45813</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45842</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45923</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45348</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45889</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45573</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45894</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45825</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45812</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45247</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45715</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45729</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45819</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45931</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45695</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>44999</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45427</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45909</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45909</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45909</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45071</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45702</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44995</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44964</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45335</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45916</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>44825</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44614</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45923</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45923</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45026</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45925</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45925</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45925</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45925</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>45923</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45924</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>45929</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45929</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45248</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45926</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45929</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45929</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45054</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45091</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45715</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45484</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45538</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45185</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44966</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45153</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45156</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>45947</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45726</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>45726</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44565</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45952</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45412</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45952</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45714</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45054</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45959</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45624</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45771</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>44830</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45958</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45961</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45961</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45961</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45961</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45547</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>44470</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45961</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>45961</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>45961</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45238</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45965</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45964</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45477</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>46153</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46153</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45248</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45168</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>45190</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>46005</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>44474</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45477</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45980</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45153</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45315</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>45982</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>44958</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45180</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45744</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>44970</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45278</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>44881</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45268</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44928</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>45742</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45834</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45302</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45628</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45691</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46162</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44530</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44530</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45566</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45566</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45103</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45995</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45999</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44740</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>45239</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45477</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>44537</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>46005</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45149</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45149</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>45054</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>46169</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>46169</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>46010</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46169</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45188</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>46169</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>45185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45194</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45050</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45307</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45594</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>46169</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46170</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45135</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46020</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45016</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45271</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>44498</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46170</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45194</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>44719</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>45237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>44592</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>44831</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44732</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>46034</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44502</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45511</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45340</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45340</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45359</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46034</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45081</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44951</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45390</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46171</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>46043</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>46043</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>44889</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>46043</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46044</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45168</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46171</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45573</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46044</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46044</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>46171</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46048</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>46175</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46175</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>46175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45048</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>46176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46050</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46050</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>44901</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45378</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46058</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>46058</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45156</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45328</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46058</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>44916</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>46058</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46062</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>45559</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>46063</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>46062</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46065</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44816</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>46182</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>46181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>46066</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>46182</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>46182</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45690</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46066</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>46076</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>46183</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>46078</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>44526</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>46183</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46183</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>46076</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46184</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45168</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46184</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>46184</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>46183</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>46183</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>46185</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46083</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45104</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45360</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45532</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>44482</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45194</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46188</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45238</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46185</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45280</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45615</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>44831</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>46035</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46195</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45477</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45541</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>46195</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45209</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>44998</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45174</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45189</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46196</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>46196</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45170</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44880</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>46105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45447</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>46111</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46112</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45610</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45266</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>46111</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45049</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>44994</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>44994</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>44529</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>44952</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>44546</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45370</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45271</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>45099</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45580</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45152</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45638</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45252</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45134</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>46247</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44564</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45152</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44999</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45908</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45104</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45016</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45834</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>46136</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45748</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46205</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>45016</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>45940</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45216</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45831</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45391</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>45391</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45257</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45693</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45693</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45455</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>44994</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45340</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45019</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45408</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45168</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45420</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45703</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45610</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>44725</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50555,7 +50555,7 @@
         <v>45129</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>45092</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45260</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45260</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45147</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>46211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45642</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45096</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45168</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>46211</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45439</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>46211</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>46211</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>46211</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45081</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45309</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>46259</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>45691</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44862</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46259</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52103,7 +52103,7 @@
         <v>45273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45247</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52249,7 +52249,7 @@
         <v>46052</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>46259</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>45019</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>44530</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>46213</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52614,7 +52614,7 @@
         <v>46213</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45250</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>46213</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45681</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>45681</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45638</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53057,7 +53057,7 @@
         <v>45216</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45524</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>45646</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45318</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45129</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>44725</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45755</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>45755</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>46267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>44999</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44928</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>44928</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45566</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>45229</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45153</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>45706</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>46269</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>46272</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54396,7 +54396,7 @@
         <v>46272</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46272</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45771</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>46272</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>46272</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45714</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54834,7 +54834,7 @@
         <v>45727</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>46281</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54980,7 +54980,7 @@
         <v>46281</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>46281</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55126,7 +55126,7 @@
         <v>46281</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>45735</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45799</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>45638</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45649</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55496,7 +55496,7 @@
         <v>45743</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45321</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55642,7 +55642,7 @@
         <v>45637</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45539</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45803</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>45803</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         <v>45539</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45810</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56080,7 +56080,7 @@
         <v>45604</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45442</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>45810</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45827</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45827</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45827</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>45827</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45827</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45827</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45831</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45833</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45843</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>44655</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>45621</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>45813</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57185,7 +57185,7 @@
         <v>45826</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>45505</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>45852</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>45013</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>45476</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>44546</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45106</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>44916</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57769,7 +57769,7 @@
         <v>45477</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57842,7 +57842,7 @@
         <v>45477</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>45477</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>44600</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58066,7 +58066,7 @@
         <v>45384</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58139,7 +58139,7 @@
         <v>44796</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58212,7 +58212,7 @@
         <v>44575</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45477</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
         <v>44656</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>45476</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45476</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58577,7 +58577,7 @@
         <v>44638</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>44797</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45071</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45476</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45741</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45743</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>45723</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>45741</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45741</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>45821</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45839</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45845</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45848</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45848</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45848</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45965</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>46001</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46111</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46273</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>46274</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>46274</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44468</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45477</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45399</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45548</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45891</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45541</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45400</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45026</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45466</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45399</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45369</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44822</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44641</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45420</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45399</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45961</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>46269</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>46280</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44490</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>46041</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>46083</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45690</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45723</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44559</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44876</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44893</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45702</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>46274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45324</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45393</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45512</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44942</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46050</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44705</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>46078</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45324</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45009</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45714</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45328</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>46142</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45016</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>46185</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45695</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45132</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45690</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45450</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44732</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45635</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45628</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44683</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45478</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45755</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45839</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>46171</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46273</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44609</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44564</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44827</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44833</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44520</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44608</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44676</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44480</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44809</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44532</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44536</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44482</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>44705</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44631</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44490</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44831</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44488</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44833</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>44831</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44526</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44490</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44811</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44827</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44490</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44683</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44755</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44593</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44496</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44473</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44519</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44519</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44520</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44532</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44532</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44617</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44552</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44686</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44825</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>44526</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44612</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44794</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44531</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44484</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44712</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45197</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45335</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45335</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45340</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45340</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45079</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44901</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45360</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45391</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44880</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45129</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44928</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45477</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44862</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45271</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>46020</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45135</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44526</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44470</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>46034</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>45735</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>45505</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45813</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45842</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44530</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45755</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45610</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45894</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45439</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45414</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45085</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>44592</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45635</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45638</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45715</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46048</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>46048</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>46048</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45054</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>46048</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45538</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>46050</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46050</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45638</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45649</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>46058</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45155</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>46058</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45803</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45803</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>46058</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>46058</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46062</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45743</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45321</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46062</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45175</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44949</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>46063</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45637</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46066</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44614</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46065</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45539</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45923</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44565</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45127</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45924</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45566</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45691</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45432</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45026</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45925</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46076</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45925</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45925</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>46078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45146</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45929</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45047</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46083</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45929</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45929</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45566</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45604</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45810</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45442</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44939</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45152</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45539</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45615</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45180</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45810</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45723</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45615</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>46105</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45573</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46111</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45952</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>46111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>44830</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45958</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44831</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>46112</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45714</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44998</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45961</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45307</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45961</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45372</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45961</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45081</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45610</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>44952</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>45965</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45169</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>44831</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45703</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45973</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45642</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45016</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44981</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45238</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45511</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45908</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45842</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46136</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45889</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45455</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45819</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45918</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45939</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45923</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45216</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45184</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46008</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44526</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45923</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45812</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45783</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45831</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45834</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45149</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45702</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45713</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45999</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44991</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45442</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45225</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45477</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>46005</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45427</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45103</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>45168</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>45168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>45091</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44935</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45191</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45677</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45216</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>46008</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>46051</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>44894</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44473</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>45755</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45755</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45755</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45197</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45194</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45532</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45690</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45827</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45827</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45827</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45218</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45827</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45827</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45019</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45019</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45736</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45099</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45723</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>44564</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45831</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>44928</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46153</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45833</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46153</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45467</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45390</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45096</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46005</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>45744</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45834</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45742</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44896</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45843</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44951</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>46169</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45340</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>44519</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46169</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45152</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>46169</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45310</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45218</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45194</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46170</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46171</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44994</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44655</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46170</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>44529</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45621</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>46171</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>46175</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46175</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45813</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>44889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44530</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>46176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>44473</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45594</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45318</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44546</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>46181</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45103</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>45573</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45252</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45566</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45566</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45582</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44966</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>46183</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>46184</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>46182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45016</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>46184</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45723</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45719</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>46183</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>46183</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45439</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>46184</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>46183</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>46182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44530</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46185</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>46185</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44609</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45156</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45047</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45086</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46196</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>46196</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46035</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>46195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45826</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45205</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45681</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45168</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45054</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45420</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45169</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45341</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45852</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45505</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>44740</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45884</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46205</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45063</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45624</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45194</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>46211</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>46211</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>46211</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44547</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46211</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>46211</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>46213</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45248</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46213</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46213</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45216</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44732</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45693</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46259</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46052</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45748</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46259</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>44719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45175</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45188</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45681</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45681</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44725</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>44819</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>44826</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45194</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45239</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45257</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45268</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>45735</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45271</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45378</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45399</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>46267</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45309</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45771</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44818</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>44827</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46269</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46272</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46272</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46272</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46272</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46272</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>45237</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>45271</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>44958</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45054</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>45537</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44496</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45693</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45693</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45610</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45455</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45328</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>44537</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>45168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45209</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46281</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>46281</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45477</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>46281</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>46281</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45412</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45412</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>46043</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45524</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45691</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>46010</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45559</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>44484</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>44651</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>46162</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45185</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>46288</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>44825</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46288</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>44502</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45147</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51029,7 +51029,7 @@
         <v>44903</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>46183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>46247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>46044</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46044</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45153</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45153</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>44992</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>44824</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45412</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45360</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>44498</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45355</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45573</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>44882</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45041</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45695</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>44482</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44868</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>44994</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>44881</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45081</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>44964</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>44970</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45610</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>45481</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45180</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>45152</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45104</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45070</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45260</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45348</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45695</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45695</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>45637</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45134</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>44827</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45370</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45153</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45484</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>44958</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45488</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>44992</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45628</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45363</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>44725</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>45156</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45247</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45049</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>44794</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>45168</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>44970</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45335</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45352</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45149</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>45008</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45209</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55303,7 +55303,7 @@
         <v>45376</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>44960</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45726</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>45726</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45280</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45250</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55751,7 +55751,7 @@
         <v>44963</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55824,7 +55824,7 @@
         <v>45408</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>45370</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45730</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45580</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45447</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45477</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45016</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45129</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45278</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45190</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45229</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45743</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>45315</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>45706</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56929,7 +56929,7 @@
         <v>45771</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45727</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45714</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
         <v>45013</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>44546</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>44600</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>44575</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>44656</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>44638</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>45476</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45106</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>44916</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45477</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45477</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45477</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45384</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44796</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45477</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45476</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>45476</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>44797</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45071</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>45476</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45741</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45743</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45723</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45741</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>45741</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45821</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>45839</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45845</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45848</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>45848</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45848</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45965</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>46001</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>46111</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>46273</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>46274</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>44468</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45477</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45933</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>46213</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45399</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45548</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45891</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44474</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>45575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45541</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45400</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45950</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45026</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45466</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45399</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>45369</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>44822</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44641</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45420</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45399</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45961</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>46269</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>46280</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44490</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>46041</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>46083</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45113</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45690</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>45971</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45723</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44559</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44876</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44893</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45702</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45259</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44993</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>46274</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45324</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45393</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45512</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>44942</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46050</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44705</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>46078</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45324</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45009</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45971</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44811</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45714</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45328</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>46142</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45016</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45566</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>46185</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45695</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>45132</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45690</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45450</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44732</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45635</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45628</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44683</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45478</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45755</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45839</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>46171</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46273</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44609</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>44564</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44827</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44827</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>44833</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44520</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44564</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44608</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44676</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44480</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44809</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44532</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44536</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44468</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>44673</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44482</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>44705</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>44631</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>44490</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>44831</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44488</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44833</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44594</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>44831</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>44526</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>44490</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44811</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>44827</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>44490</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>44683</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44755</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44593</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>44496</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44473</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44519</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>44519</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44520</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>44532</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44532</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44617</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44552</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>44686</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44825</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>44526</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>44612</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44794</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>44531</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44484</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>44712</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>44645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45197</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45335</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45335</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>44749</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45174</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45340</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45340</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>44834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45359</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45050</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45079</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>44901</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45360</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45391</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44880</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45129</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44928</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45477</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44862</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45271</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>46020</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45135</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44526</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44470</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>46034</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>45735</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>45505</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45813</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45842</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44530</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45755</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45610</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45894</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45439</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45414</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45085</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>44592</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>46044</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45635</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45638</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45715</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46048</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>46048</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>46048</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45054</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>46048</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45538</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>46050</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46050</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>45799</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45909</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45638</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45649</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>46058</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45155</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>46058</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45803</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45803</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>46058</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>46058</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>46062</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45743</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45321</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46062</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45175</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44949</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44999</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>46063</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>45637</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46066</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44614</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>46065</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45539</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>45923</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44565</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45127</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45923</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45924</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45566</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45691</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45432</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46076</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45925</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46066</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45026</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45925</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46076</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45925</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45925</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>46078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45197</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45929</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45146</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>45929</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45047</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>46083</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45929</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45929</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45566</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45604</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45810</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>45442</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>44939</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45152</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45539</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>45615</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45180</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45810</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45723</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45615</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>46105</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45573</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46111</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45952</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>46111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>44830</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45958</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44831</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>46112</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45714</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>44998</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45961</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45307</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45961</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45372</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45961</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45081</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45610</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>44952</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>45965</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45169</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>44831</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45703</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45973</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45642</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45016</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45169</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44981</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44995</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45238</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45511</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45908</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45842</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46136</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45889</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45455</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45819</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>45918</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45939</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45923</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45216</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45184</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46008</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44526</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45923</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45812</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45931</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45783</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45831</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45834</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45149</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45702</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45713</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45999</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45999</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>44991</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45442</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45225</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45477</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>46005</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45427</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>45008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45103</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>45168</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>45168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45685</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>45091</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>44935</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45191</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45677</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45216</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>46008</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>46051</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>44894</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>44473</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>45755</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45755</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45755</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45197</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45194</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45532</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45690</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45827</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45827</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45827</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45071</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45218</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45827</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45827</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45019</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45019</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45736</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45099</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45723</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>44564</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>45831</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>44593</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36860,7 +36860,7 @@
         <v>44928</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46153</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>45833</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46153</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45467</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45390</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45096</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46005</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>45744</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45834</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45742</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44896</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>45843</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>44951</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>46169</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45340</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>44519</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46169</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45152</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>46169</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>45121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45310</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45391</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45218</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45194</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45182</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>46170</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46171</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44994</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>44655</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46170</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>44529</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45621</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>46171</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>46175</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>46175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46175</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45813</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>44889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44530</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40369,7 +40369,7 @@
         <v>46176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>44473</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45594</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>45318</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>44546</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>46181</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45103</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>45573</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45252</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45566</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45566</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45582</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44966</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>46183</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>46184</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>46182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45016</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>46184</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45723</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45719</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>46183</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>46183</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45439</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>46184</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>46183</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>46182</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44530</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46185</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>46185</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44609</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45156</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>45047</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45086</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>46196</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>46196</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46035</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>46195</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45826</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45205</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45681</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45168</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45054</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45420</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45169</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45341</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45852</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45505</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>44740</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45884</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>46205</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45063</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45624</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45194</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>46211</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>46211</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>46211</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44547</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46211</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>46211</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>46213</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45248</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46213</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46213</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45216</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>44732</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45693</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>46259</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46052</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>46259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45748</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46259</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>44719</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45175</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>45188</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45681</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45681</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44725</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>44819</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>44826</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45194</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45239</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45257</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45268</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46974,7 +46974,7 @@
         <v>45735</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45271</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45378</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45399</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>46267</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47339,7 +47339,7 @@
         <v>45309</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45771</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44818</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45302</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>44827</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46269</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46272</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46272</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46272</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46272</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46272</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>45237</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>45271</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>44958</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45054</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>45537</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>44496</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45693</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45693</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45610</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45455</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45328</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>44537</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>45168</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45209</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46281</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>46281</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45477</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>46281</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>46281</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>45412</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45412</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49778,7 +49778,7 @@
         <v>46043</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45524</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45691</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>46010</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45559</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>44484</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>44651</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>46162</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45185</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>46288</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>44825</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>46288</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46287</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>44502</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45147</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51029,7 +51029,7 @@
         <v>44903</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>46183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>46247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>46044</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46044</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45153</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45153</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>44992</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>44824</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45412</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45360</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>44498</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45355</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45573</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>44882</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45041</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45695</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>44482</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>44868</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>44994</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>44881</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45081</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>44964</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>44970</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45610</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>45481</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45180</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>45152</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45104</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>45070</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45260</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45348</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45695</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45695</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         <v>45637</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         <v>45134</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>44827</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45370</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>45153</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45484</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>44958</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>45488</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>44992</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45628</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45363</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54422,7 +54422,7 @@
         <v>44725</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         <v>45156</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45247</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45049</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>44794</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>45168</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>44970</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45335</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45352</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45149</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>45008</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45209</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55303,7 +55303,7 @@
         <v>45376</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         <v>44960</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55454,7 +55454,7 @@
         <v>45726</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>45726</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45280</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>45250</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55751,7 +55751,7 @@
         <v>44963</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55824,7 +55824,7 @@
         <v>45408</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>45370</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45730</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45580</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45447</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45477</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45016</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56340,7 +56340,7 @@
         <v>45129</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56413,7 +56413,7 @@
         <v>45278</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56486,7 +56486,7 @@
         <v>45190</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56559,7 +56559,7 @@
         <v>45229</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45743</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>45315</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>45706</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56929,7 +56929,7 @@
         <v>45771</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>45727</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45714</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
         <v>45013</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57221,7 +57221,7 @@
         <v>44546</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>44600</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>44575</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>44656</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>44638</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>45476</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45106</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>44916</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45477</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45477</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45477</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45384</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44796</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45477</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45476</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>45476</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>44797</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45071</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>45476</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45741</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>45743</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45723</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45741</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>45741</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45821</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>45839</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45845</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>45848</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>45848</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45848</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45965</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>46001</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>46111</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>46273</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>46274</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45026</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45369</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45466</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45385</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45399</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>44822</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>44641</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45420</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45961</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45147</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45399</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>46269</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45629</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45723</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44490</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>46083</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45702</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44876</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44559</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44893</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45484</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45755</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44519</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>44883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>45016</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>45595</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44811</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44942</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>46050</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>46078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45971</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45328</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44705</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45695</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>46142</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45450</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45352</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45755</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45009</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44876</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45594</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44732</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45690</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45225</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45393</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45635</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45671</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44683</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45478</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>46273</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44564</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44477</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>44827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44827</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44833</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44520</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44608</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44564</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44809</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44482</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44673</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44705</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44631</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44488</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44582</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44833</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44594</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44490</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>44827</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44683</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44490</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>44482</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44755</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44593</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>44519</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44519</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>44520</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44473</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>44713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44617</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44741</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44552</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44686</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44825</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44526</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44612</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44794</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44531</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44484</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44712</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44794</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45477</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44609</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44868</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44958</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45363</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45695</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45695</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45197</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45127</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44651</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45352</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45008</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45355</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44963</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45180</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45714</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45685</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45566</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44473</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45335</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45748</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>46005</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45505</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45573</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45041</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45085</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45310</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45637</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45842</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46020</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45813</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45894</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45370</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45399</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45730</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46034</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44949</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44519</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45335</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45432</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45376</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45677</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45909</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45414</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46048</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46048</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45916</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46048</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45735</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45799</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45638</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45649</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45321</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45637</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45539</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45803</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45803</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46050</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45719</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45923</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45923</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45923</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45924</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45467</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44970</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>46058</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45926</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45439</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44827</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>46058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45929</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45929</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46058</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45539</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45810</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45455</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46062</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45604</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46062</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46065</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45681</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44827</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>46065</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45735</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45616</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46066</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44593</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45477</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45146</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45412</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45341</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45442</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45218</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46066</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45615</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>46078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44975</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>46076</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45713</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45723</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>45169</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>45086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45952</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45175</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>45070</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45723</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44484</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44781</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45008</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45959</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45047</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45961</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45961</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45964</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45714</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44818</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45047</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45755</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45216</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45973</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44526</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45079</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45488</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>46105</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>46111</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>46112</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45723</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44749</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45390</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>44824</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44496</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45481</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45360</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>44834</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45442</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45827</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45209</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45582</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45827</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45827</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45218</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45827</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45372</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45999</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45827</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45160</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44939</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45121</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45152</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45168</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44882</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44819</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45833</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44991</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45908</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45348</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45573</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45834</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46136</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45748</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45940</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45216</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45831</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45247</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44999</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45259</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45843</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>46051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45918</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44964</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45335</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45939</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44825</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45842</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45923</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45889</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45825</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45026</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45412</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45819</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45923</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45923</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45248</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45931</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45937</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45427</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45813</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45054</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45071</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45715</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45702</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45484</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45538</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45169</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44655</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45621</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45185</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44966</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45153</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45813</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45726</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45726</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>44565</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45412</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45714</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45054</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>45624</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45771</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44830</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45547</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45238</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>45477</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>46153</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>46005</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45248</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45744</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45190</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45834</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44474</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45826</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45477</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>45153</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45315</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>46169</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>46169</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45180</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>46170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>44970</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45278</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45505</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45852</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44881</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45268</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>44928</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>46171</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46171</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46175</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45742</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45884</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45628</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45691</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44530</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>44530</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46182</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45566</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45566</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>46182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45103</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46183</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46183</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>46183</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>46184</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>46184</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>46184</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>46183</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46188</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44740</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46185</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45477</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44537</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45149</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46195</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45054</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45175</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46195</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46196</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46196</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45185</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45194</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45050</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45307</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45594</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45135</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45016</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45271</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44498</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45194</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44719</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45237</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44592</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44831</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>44732</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46205</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>44502</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45511</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45340</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45340</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45359</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45081</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44951</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45390</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46211</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44889</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46211</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46211</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46211</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>46259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45573</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>46259</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45225</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46259</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45048</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46213</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46213</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46213</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44901</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45378</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45156</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45328</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44916</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45559</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44816</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45690</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46269</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>46272</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>46272</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46272</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>44526</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>46272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45168</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>46272</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45360</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45532</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44482</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>46281</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46281</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45194</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>46281</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46281</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45238</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45205</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45615</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>44831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45477</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45541</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46010</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45209</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>44998</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45189</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45170</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>44880</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>46162</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45447</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46043</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45610</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45266</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46288</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46287</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45049</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44994</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>44994</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>46288</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>44529</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>46287</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44952</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>44546</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45370</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45271</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45580</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45152</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>46183</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45638</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46044</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45182</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51179,7 +51179,7 @@
         <v>45252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46292</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45134</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>44564</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>46044</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45152</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>44999</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45104</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>45016</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45016</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51987,7 +51987,7 @@
         <v>46295</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45391</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45391</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52206,7 +52206,7 @@
         <v>46295</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45257</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>46294</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45693</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45693</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         <v>46247</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>46296</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>45455</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>44994</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45340</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45019</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>46176</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>46050</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45408</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45980</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45168</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45982</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>46296</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>45420</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>45703</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45610</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>44725</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45129</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45092</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45260</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45260</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45147</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>45642</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>45096</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45168</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45439</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>45081</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45309</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45691</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45225</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>44862</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45273</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45247</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>45019</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>44530</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>45250</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>45681</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45681</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45638</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45216</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45524</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45646</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45318</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45129</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44725</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45755</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45755</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>44999</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>44928</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>44928</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45566</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>45229</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45153</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45706</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45771</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56636,7 +56636,7 @@
         <v>45013</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>45476</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>44546</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45106</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>44916</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45477</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45477</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45477</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>44600</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>45384</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44796</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>45477</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>44656</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45476</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45476</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>44638</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44797</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45476</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>45741</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45743</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45723</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45741</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45741</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45821</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45839</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45845</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>45848</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>45848</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45848</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45965</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>46001</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46111</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46273</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>46274</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44474</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45575</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45026</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45369</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45466</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45385</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45399</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>44822</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>44641</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45420</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45961</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45147</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45399</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>46269</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46280</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>44532</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45629</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45723</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44490</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>46083</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>45113</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45702</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45971</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45723</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44876</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>45259</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44559</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>44893</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45484</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44993</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45755</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44519</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>44883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>45016</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>44980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>45595</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44811</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45216</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>45624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44942</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>46050</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>46078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45971</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45328</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45714</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45566</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44705</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45695</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>46142</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45450</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45352</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45755</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45009</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44876</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45169</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45594</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44732</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45273</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45690</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45225</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45393</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45635</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45671</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44683</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45478</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45755</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>46273</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44609</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44564</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44477</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>44827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44827</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44833</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44520</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44608</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44564</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44809</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>44831</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44532</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44536</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44482</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44673</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44705</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44631</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44490</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>44831</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44488</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>44582</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44833</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44594</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44831</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44490</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>44827</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44683</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44490</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>44482</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44743</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44755</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44593</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>44519</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44519</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>44520</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44473</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>44532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>44713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44617</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44741</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44552</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44686</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44825</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44526</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44612</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>44794</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44531</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44484</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44712</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>44794</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45477</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>44609</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45063</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>44992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>45537</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>44868</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44958</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45363</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45695</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45695</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45197</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45127</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44651</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45352</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45008</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45743</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45355</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45610</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44963</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45180</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45714</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45685</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45566</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44473</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45335</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45727</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45748</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>46005</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45505</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45573</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45041</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45085</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45310</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45194</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45637</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45842</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>46020</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45813</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45894</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45370</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45399</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45730</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>46034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>44981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45729</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>46034</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44949</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>44519</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45335</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45432</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45376</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45677</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45909</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45414</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46044</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>46048</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46048</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45916</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>46048</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46048</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45735</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45799</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45638</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45649</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45743</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45321</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45637</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45539</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45803</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45803</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46050</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45719</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45923</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45923</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45923</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45924</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>45467</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>45929</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44970</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>46058</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45926</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45439</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44827</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>46058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45929</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45929</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46058</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45539</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45810</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45455</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46062</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45604</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46062</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46065</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45681</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44827</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>46065</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45735</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45616</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46066</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44593</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45477</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45146</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45412</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45341</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45442</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45218</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46066</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45615</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>46078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44975</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>46076</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45713</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45723</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27609,7 +27609,7 @@
         <v>45169</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>45086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45952</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45175</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>45070</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45723</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>44484</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44781</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45008</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45959</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45047</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45961</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45961</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45964</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45714</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44818</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45047</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45755</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45216</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45635</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45973</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44526</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45079</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45488</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>46105</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>46111</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>46112</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45723</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>44749</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45390</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>44824</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44496</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45481</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45360</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>44834</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45442</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45827</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45209</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45582</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45827</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45827</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45995</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45218</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45827</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45372</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45999</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45827</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45160</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44939</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45121</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45152</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45168</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44882</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44819</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45833</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44991</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45908</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45348</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45573</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33252,7 +33252,7 @@
         <v>45169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45834</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46136</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45748</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45940</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45216</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45831</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45247</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45695</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44999</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45259</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>46008</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45843</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>46051</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45827</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45918</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44964</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45335</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45939</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44825</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45842</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45923</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45889</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45825</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45812</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45026</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45412</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>45819</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45923</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>45923</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45248</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45931</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45937</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45427</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45813</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>45054</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45071</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45715</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45702</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45484</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45538</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45169</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44655</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45621</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45185</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44966</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45153</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45813</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45726</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45726</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>44565</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45412</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45714</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45054</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>45624</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45771</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>44830</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45547</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45238</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>45477</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>46153</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>46005</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45248</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>45744</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45190</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45834</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44474</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45826</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45477</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>45153</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45315</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38981,7 +38981,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>46169</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>46169</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45180</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>46170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>44970</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45278</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39638,7 +39638,7 @@
         <v>45505</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45852</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>44881</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>45268</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>44928</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>46171</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46171</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46175</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45742</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45884</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45628</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>45691</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44530</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>44530</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>46182</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41171,7 +41171,7 @@
         <v>46181</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>45566</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45566</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>46182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45103</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46183</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46183</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>46183</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>46184</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>46184</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>46184</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>46183</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46188</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>44740</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46185</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45477</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44537</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45149</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45149</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46195</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45054</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45175</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46195</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46196</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46196</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45185</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45194</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45050</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45307</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45594</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45135</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45016</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45271</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44498</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45194</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44719</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45237</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44592</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44831</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>44732</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46205</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>44502</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45511</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45340</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45340</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45359</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45081</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44951</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45390</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46211</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44889</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46211</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46211</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46211</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46211</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45168</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>46259</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45573</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>46259</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45225</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46259</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45048</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>46213</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46213</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>46213</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44901</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45378</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45156</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45328</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>44916</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45559</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44816</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45690</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46269</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>46272</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>46272</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46272</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>44526</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>46272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45168</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>46272</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45360</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45532</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44482</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>46281</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46281</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45194</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>46281</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46281</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45238</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45205</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45280</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45615</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>44831</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45477</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45541</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46010</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45209</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>44998</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45174</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>45189</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49198,7 +49198,7 @@
         <v>45170</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49271,7 +49271,7 @@
         <v>44880</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>46162</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45447</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46043</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45610</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45266</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46288</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46287</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45049</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44994</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>44994</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>46288</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>44529</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>46287</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44952</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>44546</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45370</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45271</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45580</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45152</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>46183</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45638</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46044</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45182</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51179,7 +51179,7 @@
         <v>45252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46292</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45134</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>44564</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51476,7 +51476,7 @@
         <v>46044</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45152</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>44999</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45104</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>45016</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45016</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51987,7 +51987,7 @@
         <v>46295</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>45391</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45391</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52206,7 +52206,7 @@
         <v>46295</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45257</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>46294</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45693</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45693</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         <v>46247</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>46296</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52727,7 +52727,7 @@
         <v>45455</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>44994</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>45340</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>45019</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>46176</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>46050</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45408</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45980</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         <v>45168</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>45982</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>46296</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>45420</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53613,7 +53613,7 @@
         <v>45703</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45610</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>44725</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53837,7 +53837,7 @@
         <v>45129</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45092</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45260</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45260</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45147</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>45642</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>45096</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45168</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45439</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>45081</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45309</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45691</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45225</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>44862</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>45273</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45247</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>45019</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>44530</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>45250</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>45681</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>45681</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45638</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>45216</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45524</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>45646</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45318</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45129</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55828,7 +55828,7 @@
         <v>44725</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55901,7 +55901,7 @@
         <v>45755</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45755</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>44999</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>44928</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>44928</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45566</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>45229</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56417,7 +56417,7 @@
         <v>45153</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45706</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45771</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56636,7 +56636,7 @@
         <v>45013</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>45476</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>44546</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45106</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>44916</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45477</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57074,7 +57074,7 @@
         <v>45477</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45477</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57220,7 +57220,7 @@
         <v>44600</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>45384</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44796</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>45477</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>44656</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45476</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45476</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>44638</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>44797</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45476</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>45741</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45743</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58252,7 +58252,7 @@
         <v>45723</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45741</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45741</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45821</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45839</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45845</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>45848</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>45848</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45848</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45965</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>46001</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46111</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>46273</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>46274</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>46274</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45575</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44551</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45399</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45385</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45466</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44822</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45399</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45147</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45961</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>46269</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45755</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45259</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>45629</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44516</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45723</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45690</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44876</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45971</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46083</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45566</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45393</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44980</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45629</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45635</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45216</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45695</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44876</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45009</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44811</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45971</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45352</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45690</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45016</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45450</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46142</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46050</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>46195</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>46185</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44683</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45478</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45477</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45848</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>46171</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46273</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44564</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44827</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>44520</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44564</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44608</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44676</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44480</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44712</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44809</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44831</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44532</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44700</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44673</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44705</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44631</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44582</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44833</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44683</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44686</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44490</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44526</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44526</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44643</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44519</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44520</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44482</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>44743</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44552</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44794</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44811</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44755</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44531</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44617</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44827</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44484</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44741</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44552</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44496</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45714</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44712</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45153</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45359</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44564</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44928</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44958</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45488</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45079</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44992</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45628</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45363</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45467</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45335</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45335</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45096</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45340</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45340</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44725</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44749</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45247</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45156</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45247</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45742</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44781</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45049</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44794</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45391</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44834</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45360</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45715</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45168</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45129</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44816</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44880</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45352</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44928</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45884</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45008</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45340</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44519</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>44960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44862</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45726</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45726</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45280</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45250</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44963</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45408</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45370</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45271</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45152</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45505</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45259</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45813</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45391</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45842</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45218</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45730</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45580</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45194</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45273</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44994</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45447</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45477</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44529</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45104</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45477</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45168</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44526</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45016</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>44889</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44530</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45278</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45729</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44530</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45229</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45715</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45743</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45439</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45414</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45085</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44928</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44592</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45909</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45318</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44546</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45160</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45638</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45909</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45706</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45103</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45573</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45252</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45566</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45566</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45054</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45582</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44966</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45771</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45538</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45016</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45723</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45719</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45439</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>44530</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45727</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45714</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45189</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45175</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44609</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44949</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45547</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44614</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44999</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45156</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45047</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45923</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45924</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45086</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45566</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45926</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45691</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45432</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45026</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45929</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45146</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45047</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45681</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45238</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45566</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45168</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45054</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45341</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44975</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45252</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45541</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44939</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45180</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>44740</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45568</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45638</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45649</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45803</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45743</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45321</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45063</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45539</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45624</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45225</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>45723</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45615</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45604</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45810</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45442</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45539</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45810</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44547</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45573</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44830</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45714</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44998</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45307</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45372</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45616</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>45081</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45610</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>44952</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45827</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45216</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45827</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45169</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44732</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45827</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45693</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45827</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>44999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45703</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45952</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45016</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45961</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44719</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45961</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45175</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45833</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45961</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45169</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45681</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45964</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45681</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45961</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45961</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44725</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>44995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45961</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>44819</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45646</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45238</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>44826</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45511</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45194</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45455</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45843</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45184</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45185</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>44526</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45239</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45257</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45268</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45735</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45271</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45149</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45713</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45378</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45399</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45771</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>44655</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44818</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45621</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45302</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44827</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44991</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45813</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45442</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45225</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45477</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45237</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45390</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45103</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45168</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45168</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45685</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45271</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>44935</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45054</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45191</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45677</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45216</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45852</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45266</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45505</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45537</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>44894</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>44496</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45693</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45693</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45610</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45455</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45755</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45328</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44537</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45168</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45209</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45197</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45194</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45532</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45690</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46105</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45477</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45218</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45248</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>46111</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45019</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45019</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45736</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45099</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45723</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45412</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>46111</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45412</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45524</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45691</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45559</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>44484</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>44651</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45995</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44825</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46005</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>44502</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45908</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45842</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44903</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>45889</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45819</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45918</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45939</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45923</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45216</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45153</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45153</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>44992</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>46008</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45923</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44824</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45412</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>45812</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>45931</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45923</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45783</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45937</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45831</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45834</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45360</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45702</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>44498</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45940</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45355</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46020</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45573</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>44882</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45041</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45695</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44482</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>44868</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44994</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>44881</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45081</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44964</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>44970</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45427</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45610</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45481</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>46034</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45827</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45180</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45152</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45748</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45070</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45260</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45348</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>46044</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>46008</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45695</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45695</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46051</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45134</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>44827</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45813</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45370</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46048</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>46048</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>46050</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45071</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46058</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46058</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>46058</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>46058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>46062</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>46063</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46066</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>46065</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>46065</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>46066</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>46153</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>46078</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>46083</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>46153</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>46005</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45744</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45834</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46169</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>46169</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>46169</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>46169</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46171</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>46171</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50156,7 +50156,7 @@
         <v>46171</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>46175</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>46175</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>46175</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>46174</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46181</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>46183</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>46184</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>46182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>46184</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>46183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>46183</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>46183</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>46182</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>46184</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46183</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>46182</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>46185</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>46185</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46188</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>46196</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>46196</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>46035</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46195</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46195</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46205</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46211</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>46211</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>46211</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>46213</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>46213</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>46213</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>46269</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>46272</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>46272</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>46272</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>46272</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>46281</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>46281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>46281</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>46281</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53471,7 +53471,7 @@
         <v>46043</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53544,7 +53544,7 @@
         <v>46010</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>46162</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>46288</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>46287</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46183</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46044</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46292</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>46294</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46169</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46294</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>46295</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>46296</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>46295</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>46296</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45980</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>46176</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>46136</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>46247</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45831</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55170,7 +55170,7 @@
         <v>46050</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45982</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>46301</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>46259</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>46259</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>46301</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>46301</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>46302</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46302</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>46259</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>46303</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>45013</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56046,7 +56046,7 @@
         <v>44546</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>44600</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>44575</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>44656</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>44638</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45476</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45106</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>44916</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45477</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45477</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45477</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56854,7 +56854,7 @@
         <v>45384</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56927,7 +56927,7 @@
         <v>44796</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45477</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>45476</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45476</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>44797</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45071</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45476</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45741</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>45743</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45723</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45741</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45741</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45821</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45839</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45845</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45848</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45848</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>45848</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>45965</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>46001</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58402,7 +58402,7 @@
         <v>46111</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58475,7 +58475,7 @@
         <v>46273</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>46274</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         <v>46274</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45575</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>44551</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45399</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45385</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45466</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44822</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45399</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45147</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45961</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>46269</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44490</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45755</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45259</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>45629</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44516</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44559</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45723</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>45690</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44876</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45971</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46083</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45566</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>45393</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45512</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44980</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45629</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45635</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45216</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44526</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45169</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44705</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45595</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45324</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45695</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44876</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45009</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44811</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45971</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45352</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45714</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>45690</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45016</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45450</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46142</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46050</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>46078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>45901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>46195</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>46185</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44683</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45478</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45477</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45848</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>46171</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46273</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44564</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44827</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>44520</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44564</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44608</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44676</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44480</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44712</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44809</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44831</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44532</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44700</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44673</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44705</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44631</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44490</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44831</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44582</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44833</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44594</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44831</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>44683</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44686</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44490</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44526</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44490</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44526</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44643</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44519</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44520</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44482</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>44743</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44612</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>44552</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>44794</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44811</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>44755</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44531</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44617</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44827</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44484</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44741</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44552</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>44496</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45714</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44712</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45153</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45359</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44564</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44593</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>44928</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44958</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45488</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45079</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>44992</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45628</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45363</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45467</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45390</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45335</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45335</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45096</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45340</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45340</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45197</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>44725</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44749</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45247</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45156</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45247</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45742</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44781</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45049</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44794</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45391</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44834</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45360</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45715</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45168</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45129</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44816</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44880</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>44951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45352</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44928</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45884</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45008</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45340</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44519</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>44960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44862</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45726</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45726</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45280</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45250</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44963</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45408</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45370</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45271</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45152</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45121</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45505</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45259</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45813</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45391</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45842</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45218</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45730</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45580</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45194</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45273</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44994</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45447</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45477</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>44529</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45104</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45477</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45168</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44526</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45016</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>44889</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44530</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45278</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45729</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44530</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45229</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45715</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45743</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45439</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45414</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45085</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45315</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44928</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44592</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45909</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45318</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44546</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45160</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45638</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45909</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45909</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45706</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45103</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45573</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45252</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45566</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45566</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45054</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45582</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44966</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45771</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45538</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>45016</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45723</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45719</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45439</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>44530</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45727</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45714</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45189</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45175</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>44609</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44949</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45547</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44614</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>44999</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45156</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45047</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45923</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45923</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45924</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>45086</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45566</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45926</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45691</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45432</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45026</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45929</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45197</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45146</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45047</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45681</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45238</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45566</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45168</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45054</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>45341</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44975</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45252</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45541</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>44939</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45615</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45180</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>44740</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45568</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45638</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45649</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45803</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45743</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45321</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45063</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45539</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45624</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45225</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>45723</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45615</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45604</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45810</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45442</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45539</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45810</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44547</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45573</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44830</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45248</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45714</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44998</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45307</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45372</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45616</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>45081</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45610</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>44952</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45827</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45216</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45827</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45827</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45169</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44732</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45827</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45693</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45827</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>44999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45703</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45952</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>45958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>45642</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45016</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45961</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>45961</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44719</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45961</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45175</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45833</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45961</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45169</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44981</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45681</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45964</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45681</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45961</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45961</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>44725</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>44995</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45961</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>44819</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45646</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45238</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>44826</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>45511</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45194</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44999</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45455</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45843</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45184</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45185</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>44526</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45973</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45239</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45257</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45268</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45735</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45271</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45149</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45713</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45378</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45399</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45771</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>44655</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44818</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45621</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45302</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44827</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44991</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45813</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45442</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45225</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45477</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45237</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45390</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45103</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45168</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>45168</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45685</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45271</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>44935</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45054</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45191</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>45677</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45216</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>45852</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>45266</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45505</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45537</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>44894</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>44496</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45693</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45693</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45610</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45455</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>45755</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45328</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44537</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45168</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45209</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45197</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45194</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45532</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45690</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46105</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45477</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45218</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45248</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>46111</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45019</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45019</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45736</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45099</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45723</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45412</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>46111</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45412</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45524</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45691</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45559</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>44484</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>44651</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45995</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45999</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45999</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45092</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44825</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46005</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>44502</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45908</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45842</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>45147</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44903</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>45889</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>45819</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45918</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45939</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45923</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45216</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>45153</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45153</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>44992</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44251,7 +44251,7 @@
         <v>46008</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44324,7 +44324,7 @@
         <v>45923</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44397,7 +44397,7 @@
         <v>44824</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45412</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>45812</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>45931</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45923</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45783</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         <v>45937</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44908,7 +44908,7 @@
         <v>45831</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45834</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45360</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45702</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>44498</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45940</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45355</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46020</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45573</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>44882</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45041</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>45695</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44482</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>44868</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44994</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>44881</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45081</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>44964</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>44970</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45427</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>45610</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45481</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>46034</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45827</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45180</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45152</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45748</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>45070</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47045,7 +47045,7 @@
         <v>45825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45260</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45348</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>46044</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>46008</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45695</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45695</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>46051</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47722,7 +47722,7 @@
         <v>45637</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45134</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>44827</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45813</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45370</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46048</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46048</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>46048</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>46050</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45071</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46058</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>46058</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>46058</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>46058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>46062</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>46063</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>46066</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>46065</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>46065</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>46066</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>46153</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>46078</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49353,7 +49353,7 @@
         <v>46083</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>46153</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>46005</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45744</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45834</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46169</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>46169</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>46169</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49937,7 +49937,7 @@
         <v>46169</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50010,7 +50010,7 @@
         <v>46171</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>46171</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50156,7 +50156,7 @@
         <v>46171</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>46175</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>46175</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>46175</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>46174</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46181</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>46183</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>46184</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>46182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>46184</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>46183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>46183</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>46183</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>46182</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>46184</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46183</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>46182</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>46185</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>46185</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46188</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>46196</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>46196</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>46035</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>46195</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>46195</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>46205</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46211</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>46211</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46211</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>46211</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>46213</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>46213</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>46213</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>46267</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>46269</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>46272</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>46272</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>46272</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>46272</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
         <v>46272</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53179,7 +53179,7 @@
         <v>46281</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53252,7 +53252,7 @@
         <v>46281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53325,7 +53325,7 @@
         <v>46281</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>46281</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53471,7 +53471,7 @@
         <v>46043</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53544,7 +53544,7 @@
         <v>46010</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>46162</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>46288</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53836,7 +53836,7 @@
         <v>46287</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>46183</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>46044</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54206,7 +54206,7 @@
         <v>46292</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54279,7 +54279,7 @@
         <v>46294</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54352,7 +54352,7 @@
         <v>46169</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46294</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>46295</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>46296</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54649,7 +54649,7 @@
         <v>46295</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>46296</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45980</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>46176</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>46136</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>46247</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45831</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55170,7 +55170,7 @@
         <v>46050</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45982</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>46301</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>46259</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>46259</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>46301</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>46301</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>46302</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46302</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>46259</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>46303</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>45013</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56046,7 +56046,7 @@
         <v>44546</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>44600</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>44575</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>44656</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>44638</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45476</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>45106</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>44916</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45477</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45477</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45477</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56854,7 +56854,7 @@
         <v>45384</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56927,7 +56927,7 @@
         <v>44796</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45477</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>45476</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45476</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>44797</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45071</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45476</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45741</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>45743</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45723</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45741</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45741</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45821</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45839</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45845</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45848</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45848</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>45848</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>45965</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>46001</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58402,7 +58402,7 @@
         <v>46111</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58475,7 +58475,7 @@
         <v>46273</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>46274</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         <v>46274</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45790</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44551</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45369</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45385</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45399</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44822</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45466</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45961</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45147</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>46269</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45723</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>44490</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45971</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44876</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>46083</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44917</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44893</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46296</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45132</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45016</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44980</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45595</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45324</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45328</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>46142</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45714</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45566</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45695</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45450</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45901</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46050</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>46078</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>46195</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44526</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45169</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>45594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44732</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45273</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45690</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45225</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>46185</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45671</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44683</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45478</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45477</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45848</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>46171</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46273</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44564</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44827</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>44520</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44564</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44608</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44676</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44712</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44809</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44700</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44705</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44673</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44631</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44490</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44831</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44831</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44488</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44582</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44526</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44811</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44827</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44490</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44683</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44743</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44552</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44755</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44593</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44520</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44713</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44617</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44686</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44526</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44612</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44794</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44712</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44794</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45477</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44992</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45537</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>44609</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44868</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45363</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45695</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45695</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45197</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44651</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45352</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45743</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>44963</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45180</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45566</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45355</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45335</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45041</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45191</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45637</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45310</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45194</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45184</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45370</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45399</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45730</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45376</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44519</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45335</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45677</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45103</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45197</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45432</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45271</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45414</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45685</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45693</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45719</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44827</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45568</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45467</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44970</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45681</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44827</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45616</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45455</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45735</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45155</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>44593</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45477</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45341</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45218</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44975</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45615</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45412</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45723</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45008</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45713</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45070</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45723</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45047</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44781</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45714</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44818</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45047</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45635</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44526</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45079</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45488</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45723</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44749</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44826</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45783</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45390</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>44824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45505</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44496</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45481</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45360</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45884</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45827</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45918</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44834</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45442</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45923</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45209</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45582</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45218</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45813</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45372</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45812</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44547</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45894</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44939</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45152</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45168</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44882</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45197</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45819</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44819</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45923</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45923</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45931</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45427</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44991</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45702</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45573</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45715</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45729</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45169</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45909</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45909</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45695</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44614</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45259</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45923</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44995</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>45335</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44825</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45929</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45026</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45412</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45054</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46005</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45715</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45538</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45169</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45961</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45961</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45961</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45961</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45961</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45961</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45961</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45185</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45744</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44966</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45961</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45153</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>45964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45834</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45726</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45726</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44565</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45973</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45714</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45054</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45624</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45771</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44830</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45547</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45238</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45477</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45168</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45190</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46169</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46169</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>46169</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45995</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45999</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45477</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45153</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45315</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44958</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45180</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>46005</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>44970</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45278</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44881</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>46171</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44928</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45742</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45302</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>46171</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45628</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45691</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46020</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44530</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>45566</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>46175</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>46175</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>45103</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>46175</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46034</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>44740</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45239</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45477</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>46044</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46182</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>46048</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44537</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46048</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46048</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45149</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45149</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46050</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45054</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46182</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45175</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>46182</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45188</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>46183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>46183</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>46183</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>46183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>46058</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45185</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46058</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>46184</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46058</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45194</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45050</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46058</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45307</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45594</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>46184</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46063</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>46062</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>46065</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>46065</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46183</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>46185</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45135</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45016</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45271</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44498</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>46066</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45194</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44719</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44592</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44732</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>46185</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44502</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45511</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45340</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45340</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45359</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45081</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>44951</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>46083</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45390</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>44889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>46035</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45573</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45225</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45048</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>46195</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>44901</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45378</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46105</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>46196</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>46111</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>46112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46111</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45156</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45328</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44916</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45559</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>44816</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45690</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>44526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45168</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45908</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46205</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45834</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45104</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45360</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45532</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45748</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45940</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45216</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45238</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45831</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45280</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45615</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>45477</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45541</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46211</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45209</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>44998</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45174</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45189</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45170</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>46211</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>46211</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44880</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>46211</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>46213</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>46213</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46213</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>45447</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45610</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45266</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45049</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>44994</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>44529</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>44952</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>44546</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45370</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46272</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45099</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45580</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46272</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45152</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46272</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45638</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45252</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45134</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>44564</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45152</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>44999</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45104</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45016</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45016</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>46281</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45391</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45391</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45257</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>46281</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>46281</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45693</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45693</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45455</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44994</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45340</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45019</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45408</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45168</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>46010</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45420</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45703</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45610</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>44725</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>46162</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45129</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45092</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46043</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45260</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46287</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45260</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45147</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45642</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45096</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45168</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>45439</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46288</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>46287</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45081</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45309</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>45691</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45225</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>44862</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45273</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45247</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>46169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>45019</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49489,7 +49489,7 @@
         <v>46183</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>44530</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46044</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45250</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46292</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>45681</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>45681</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>46044</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45638</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45216</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>45524</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45646</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>46294</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>46295</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>46295</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>45318</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>46294</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50735,7 +50735,7 @@
         <v>45129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>44725</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45755</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45755</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>46247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>44999</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46176</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>46050</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45980</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>45982</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46296</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51621,7 +51621,7 @@
         <v>44928</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>44928</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45566</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45229</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45153</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45831</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>45706</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46136</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45771</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>46301</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>46301</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>46301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45714</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45727</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>46259</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46302</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>46303</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>46259</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>46302</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46259</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45735</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45799</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45638</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45649</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45743</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45321</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45637</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>46308</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45539</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45803</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45803</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>46308</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45539</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45810</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45604</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45442</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45810</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>46267</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46310</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>46310</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46269</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45827</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>45827</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45827</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45827</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>46310</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>46310</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45827</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45827</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45833</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45843</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>44655</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45621</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>45826</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45505</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>45852</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45013</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45476</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>44546</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45106</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>44916</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45477</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45477</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45477</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>44600</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56484,7 +56484,7 @@
         <v>45384</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>44796</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>44575</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45477</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>44656</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56849,7 +56849,7 @@
         <v>45476</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45476</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>44638</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>44797</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57141,7 +57141,7 @@
         <v>45071</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45476</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45741</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         <v>45743</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45723</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45741</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45741</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>45821</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45839</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45845</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45848</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>45848</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>45848</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58100,7 +58100,7 @@
         <v>45965</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>46001</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>46111</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>46273</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>46274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>46274</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45399</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45541</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45790</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44551</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45541</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45369</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45385</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45399</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44822</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45466</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45961</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45147</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45399</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>46269</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45629</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45723</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>44490</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>45690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45971</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>45702</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45723</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44876</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>46083</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45259</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44917</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44893</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46296</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>45484</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44993</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46274</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45132</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45016</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44980</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45595</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44811</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>45216</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>45324</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45328</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>46142</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45714</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45566</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45695</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45971</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45450</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45901</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46050</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>46078</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45009</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>46195</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44526</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44876</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45169</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>45594</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44732</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45273</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45690</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>45225</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45393</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>46185</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>45671</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44683</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45478</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45477</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>45839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45848</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>46171</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46273</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44564</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>44827</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44827</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>44520</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44564</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>44608</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>44676</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44712</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44809</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44831</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44532</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44700</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44705</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44673</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44631</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44490</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44831</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44831</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44488</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44582</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>44833</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>44594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44526</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44811</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44827</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44490</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44683</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>44743</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>44552</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44755</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44593</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44496</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>44520</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44532</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>44532</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44713</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44617</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44686</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>44526</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44612</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44794</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44712</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>44794</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>45477</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44992</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45063</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45537</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>44609</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44868</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45363</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45695</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45695</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45197</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44651</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45352</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45610</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45743</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>44963</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45180</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45566</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45355</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45335</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45041</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45191</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45637</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45310</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45194</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45184</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45370</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45399</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45730</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45376</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44949</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44519</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45335</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45677</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45103</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45197</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45432</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45271</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45414</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45685</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44894</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45693</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45719</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44827</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45568</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45467</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44970</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45681</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44827</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45616</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>45455</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45735</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45155</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>44593</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45477</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45146</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45341</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45218</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44975</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45615</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45412</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45723</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45008</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45713</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45070</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45723</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45047</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44781</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45714</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44818</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45047</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45635</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45755</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>44526</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45079</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45488</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45723</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44749</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44826</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45783</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45390</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>44824</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45505</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>44496</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45481</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45360</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45884</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45827</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45918</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>46008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44834</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45442</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45939</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45923</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45209</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45582</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45218</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45842</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45813</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45372</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45812</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44547</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45894</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44939</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45152</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45168</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44882</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45197</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45819</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>44819</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45252</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45923</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45923</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45931</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45427</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44991</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45702</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45573</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45715</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45729</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45169</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45909</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45909</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45916</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45247</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45695</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>44614</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45259</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45923</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44995</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>44964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>45335</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45926</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>44825</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45929</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45929</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45026</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45412</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45054</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46005</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45715</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45484</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45538</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45169</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45961</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45961</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45961</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45961</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45961</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45961</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45961</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45185</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45744</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44966</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45961</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45153</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>45964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45834</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>45726</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45726</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44565</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45973</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45714</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45054</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45624</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45771</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44830</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45547</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45238</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45477</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>45248</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45168</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45190</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>46169</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>46169</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>46169</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45995</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45999</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45477</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45153</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45315</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44958</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45180</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>46005</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>44970</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45278</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44881</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>45268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>46171</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>44928</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45742</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45302</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>46171</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45628</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45691</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46020</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44530</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>44530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>45566</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>45566</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>46175</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>46175</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35134,7 +35134,7 @@
         <v>45103</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>46175</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46034</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35353,7 +35353,7 @@
         <v>44740</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45239</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45477</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>46044</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46182</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>46048</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44537</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46181</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46048</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46048</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45149</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>45149</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46050</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45054</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46182</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>45175</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>46182</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45188</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>46183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>46183</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>46183</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>46183</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>46058</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45185</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>46058</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>46184</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>46058</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45194</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45050</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46058</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45307</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>45594</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>46184</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46063</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>46062</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>46065</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>46065</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46183</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>46185</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45135</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45016</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45271</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44498</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>46066</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45194</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44719</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44592</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>46066</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>44732</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>46185</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44502</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45511</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45340</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45340</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45359</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45081</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>44951</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>46083</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45390</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>44889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>46035</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45573</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>46195</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>45225</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45048</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>46195</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>44901</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45378</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46105</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>46196</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>46111</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>46112</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46111</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>45156</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>45328</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44916</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45559</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>44816</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45690</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>44526</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45168</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>45908</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46205</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45834</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41968,7 +41968,7 @@
         <v>45104</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45360</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45532</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45748</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45940</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45216</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45238</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45831</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45280</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45615</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>44831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>45477</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45541</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46211</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45209</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>44998</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45174</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45189</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45170</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43604,7 +43604,7 @@
         <v>46211</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>46211</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44880</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>46211</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>46213</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>46213</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46213</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>45447</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45610</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44261,7 +44261,7 @@
         <v>45266</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45049</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
         <v>44994</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44480,7 +44480,7 @@
         <v>44994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>44529</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>44952</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>44546</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>45370</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>46272</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>45271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45099</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45210,7 +45210,7 @@
         <v>45580</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>46272</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45152</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>46272</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45638</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>45182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>45252</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45134</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>44564</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45152</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>44999</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45104</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45016</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45016</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>46281</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45391</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45391</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45257</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>46281</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>46281</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45693</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45693</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45455</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>44994</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45340</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45019</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45408</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45168</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>46010</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45420</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45703</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45610</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>44725</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>46162</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45129</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45092</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46043</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>46288</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45260</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>46287</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>45260</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45147</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45642</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45096</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45168</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>45439</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46288</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>46287</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45081</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45309</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>45691</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45225</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>44862</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45273</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45247</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49343,7 +49343,7 @@
         <v>46169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         <v>45019</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49489,7 +49489,7 @@
         <v>46183</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>44530</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46044</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45250</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>46292</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>45681</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>45681</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>46044</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>45638</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45216</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>45524</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45646</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>46294</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>46295</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>46295</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>45318</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>46294</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50735,7 +50735,7 @@
         <v>45129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50808,7 +50808,7 @@
         <v>44725</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45755</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45755</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>46247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>44999</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46176</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>46050</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45980</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>45982</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>46296</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51621,7 +51621,7 @@
         <v>44928</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>44928</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45566</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45229</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45153</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45831</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>45706</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52142,7 +52142,7 @@
         <v>46136</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52215,7 +52215,7 @@
         <v>45771</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52288,7 +52288,7 @@
         <v>46301</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>46301</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>46301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52507,7 +52507,7 @@
         <v>45714</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>45727</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52653,7 +52653,7 @@
         <v>46259</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>46302</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>46303</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>46259</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>46302</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46259</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45735</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>45799</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45638</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>45649</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45743</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>45321</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45637</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53607,7 +53607,7 @@
         <v>46308</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45539</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53753,7 +53753,7 @@
         <v>45803</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45803</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53899,7 +53899,7 @@
         <v>46308</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>45539</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>45810</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45604</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45442</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45810</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54342,7 +54342,7 @@
         <v>46267</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54415,7 +54415,7 @@
         <v>46310</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>46310</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46269</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54654,7 +54654,7 @@
         <v>45827</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>45827</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45827</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45827</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>46310</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>46310</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55092,7 +55092,7 @@
         <v>45827</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45827</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45833</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>45843</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55384,7 +55384,7 @@
         <v>44655</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45621</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>45826</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45505</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>45852</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45013</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>45476</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>44546</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45106</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>44916</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56187,7 +56187,7 @@
         <v>45477</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45477</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45477</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>44600</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56484,7 +56484,7 @@
         <v>45384</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>44796</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>44575</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45477</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>44656</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56849,7 +56849,7 @@
         <v>45476</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45476</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>44638</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>44797</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57141,7 +57141,7 @@
         <v>45071</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>45476</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45741</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         <v>45743</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45723</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45741</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45741</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>45821</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45839</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45845</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45848</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>45848</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>45848</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58100,7 +58100,7 @@
         <v>45965</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>46001</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>46111</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>46273</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>46274</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>46274</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45541</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45541</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45466</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45399</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45385</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44822</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45399</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45961</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46269</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46083</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45813</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>46296</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45971</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>45723</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45690</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45723</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>44917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45484</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>45755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>46274</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45324</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>45450</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45393</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45755</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45971</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45635</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44942</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>46050</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>46078</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45216</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45328</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44705</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>46142</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45595</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45324</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45009</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45225</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45016</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45566</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45755</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45273</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45695</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45132</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45690</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44683</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45671</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45478</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45477</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45839</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45848</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>46171</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46273</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44564</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44827</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44827</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44520</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44564</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44676</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44712</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44831</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44536</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44839</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44700</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44673</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44705</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44831</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44582</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44833</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44594</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44594</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44526</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44811</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44827</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44683</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44552</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44755</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44593</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44496</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44519</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44519</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44520</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44532</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44617</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44741</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44686</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44825</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44526</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44643</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44612</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44794</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44531</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45505</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44712</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44502</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44645</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45842</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>44903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45050</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45335</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45335</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45340</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45340</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45247</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>44781</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44824</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44834</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45412</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45715</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45729</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45360</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45714</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>44498</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45715</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45355</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>45041</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>45695</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45909</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45834</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45081</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44970</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45610</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45152</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44614</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45923</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45923</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45924</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45260</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45926</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>46169</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46169</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>46169</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45929</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45929</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45348</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46171</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45695</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45637</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45134</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>46171</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>46175</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45370</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45079</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46175</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46175</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>46174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45153</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44901</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45484</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45391</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45360</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45129</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45488</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>44992</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45628</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44816</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45363</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44725</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46183</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46183</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46182</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46184</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45247</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44880</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44794</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45959</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45961</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45961</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45961</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45961</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45961</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45961</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45961</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45961</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45168</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45965</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44970</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>46196</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46035</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45352</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>46195</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>46195</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45008</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45209</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45973</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45376</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45726</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45726</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44963</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44928</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45408</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45370</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45730</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45580</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45477</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45447</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45477</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45477</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45016</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45129</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45278</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45190</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46211</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>46211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45229</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>46211</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45743</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46211</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46213</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44862</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>46213</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45995</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45315</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44928</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45706</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>46005</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>45771</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45271</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>46281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>46020</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>46281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>46043</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>46034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46010</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>46162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46288</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>46287</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46044</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46287</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45735</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>46048</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46048</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46044</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46048</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45799</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45638</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46050</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45803</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45803</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45135</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45743</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45321</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45637</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45539</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45604</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45810</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46058</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46058</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45442</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46058</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46292</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45810</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46062</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46066</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46065</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>46065</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>46294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46169</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>46294</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46066</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>46295</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>46078</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>46296</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>46295</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45827</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45827</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>46083</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45827</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45827</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>46296</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45980</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45477</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45833</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>46136</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46247</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45831</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>46050</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44526</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45982</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45843</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46301</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46301</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44530</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>46302</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>46302</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>46259</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>46112</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>44655</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45621</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45610</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45439</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45414</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45085</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45826</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>46308</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45852</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45505</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44916</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>46308</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44592</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45884</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45635</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45638</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45908</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45842</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45054</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45538</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45889</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45918</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45939</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45923</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45216</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>46008</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45923</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45812</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45931</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45923</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>46310</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45155</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45783</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>46310</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>46310</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45937</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45702</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45940</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>46310</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>46267</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45175</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>44949</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45547</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44999</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46272</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44565</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45127</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45427</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45827</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46269</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45691</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45432</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45748</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45026</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46272</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45825</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45197</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45146</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>46272</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>46008</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45047</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>46051</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45238</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45566</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44975</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>45813</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45252</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45541</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44939</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45152</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45180</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45568</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45225</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45723</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45615</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46153</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>44994</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>46153</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45573</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>44830</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>46005</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45714</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45744</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>44998</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45307</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45372</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45081</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45610</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44952</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45169</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44999</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>44831</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45703</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45642</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45016</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45169</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44981</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44995</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45646</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45238</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45511</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44999</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45455</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45184</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45185</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>44526</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45149</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45713</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44991</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45442</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45225</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45477</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45390</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45008</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45103</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45168</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45168</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45685</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45091</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>44935</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45191</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45677</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45216</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>44894</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45755</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45755</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45755</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45197</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>45194</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45532</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45690</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45218</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45248</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45019</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45019</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45736</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45099</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45723</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>44564</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44593</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44928</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45638</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45467</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45390</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45096</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45742</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>44896</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45170</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>44951</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>45340</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>44519</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45152</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45121</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45310</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45259</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45391</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45218</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45194</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45182</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>44994</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>44529</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44889</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>44530</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45594</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45318</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44546</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45160</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45103</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45573</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45252</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45566</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45566</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45582</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>44966</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45016</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45723</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45719</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45439</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>44530</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50330,7 +50330,7 @@
         <v>44609</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45156</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45047</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45086</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45205</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45681</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45168</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45054</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>45420</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45341</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44740</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>45063</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>45194</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>44547</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45616</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45216</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>44732</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>45693</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45748</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>44719</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45188</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52160,7 +52160,7 @@
         <v>45681</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45681</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>44725</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44819</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44826</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45194</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45239</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45257</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45268</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45735</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45271</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52968,7 +52968,7 @@
         <v>45378</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>45399</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53114,7 +53114,7 @@
         <v>45309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45771</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>44818</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45302</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>44827</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45237</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>45271</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>44958</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>45054</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45266</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45537</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>44496</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>45693</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45693</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45610</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45455</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45328</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>44537</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>45168</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45209</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45477</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45412</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45412</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45524</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45691</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45559</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>44651</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45092</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45185</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>44825</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45013</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>44546</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>44600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>44575</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>44656</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>44638</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45476</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45106</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>44916</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45477</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45477</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45477</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45384</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>44796</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>45477</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45476</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45476</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>44797</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45071</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45476</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45741</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45743</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>45723</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45741</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45741</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45821</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45839</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45845</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45848</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45848</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45848</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45965</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>46001</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46111</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>46273</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46274</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46274</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -601,7 +601,7 @@
         <v>45040</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>45477</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>45933</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>46213</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>45541</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>45399</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45891</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45575</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>45541</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>45790</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45026</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45466</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45399</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45385</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44822</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44641</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45420</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45917</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45399</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45961</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>46269</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>46280</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44532</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44893</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45702</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45259</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>45629</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46083</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45813</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>46296</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45971</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>45723</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45690</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>45723</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>44917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45484</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44993</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>45755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>46274</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45324</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>45450</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45393</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45755</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45965</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45971</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>45629</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45635</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45628</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44942</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>46050</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>46078</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45216</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45328</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44705</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>46142</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45595</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>45324</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45009</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45225</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45016</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45566</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45755</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45273</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45695</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45132</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45690</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44683</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45671</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45478</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45477</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45839</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45848</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>46171</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46273</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44564</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44827</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44827</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44520</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44564</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44676</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44712</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44831</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44532</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44536</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44839</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44700</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44673</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44705</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44831</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44582</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44833</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44594</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44594</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44526</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44811</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>44827</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44683</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44743</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>44552</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44755</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>44593</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44496</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>44519</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44519</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>44520</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>44532</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44532</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44713</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44617</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>44741</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44686</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>44825</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44526</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44643</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44612</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44794</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44531</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45505</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44712</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44502</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44645</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45842</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45147</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>44903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45050</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45335</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45335</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45340</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45340</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45197</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45247</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45894</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>44781</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44992</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44824</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44834</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45412</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45715</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45729</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45360</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45714</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>44498</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45715</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45355</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>44882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>45041</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>45695</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45909</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45834</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44868</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45359</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45081</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>44964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44970</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45610</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45481</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45916</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45152</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>44614</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45923</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45104</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45923</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45924</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20163,7 +20163,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45260</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45926</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>46169</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>46169</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>46169</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45929</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>46169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45929</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45348</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>46171</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45695</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45637</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45134</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>46171</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>46175</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>45370</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45079</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46175</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46175</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>46174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45153</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44901</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45484</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45391</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45360</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45129</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45488</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>44992</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45628</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44816</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45363</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44725</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45952</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>46184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>46183</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46183</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46183</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46182</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46184</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45958</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45247</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>44880</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44794</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46185</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45959</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45961</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45961</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45961</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45961</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45961</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>45961</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45961</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45961</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45168</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45965</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44970</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45335</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>46196</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46196</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46035</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45352</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>46195</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>46195</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>45149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45008</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45209</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45973</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45376</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45726</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45726</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45280</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26843,7 +26843,7 @@
         <v>44963</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44928</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45408</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45370</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45730</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45580</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45477</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45447</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45477</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45477</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45016</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45129</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45278</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45190</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46211</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>46211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45229</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>46211</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45743</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>46211</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46213</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44862</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>46213</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>45995</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>45999</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45315</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44928</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>45706</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>46005</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>45771</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45271</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>46281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>46020</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>46281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>46043</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>46034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46010</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>46162</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46288</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>46287</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46044</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46287</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45735</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>46048</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46048</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46044</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46048</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45799</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45638</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46050</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45803</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45803</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45135</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45743</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45321</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45637</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45539</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45604</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45810</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>46058</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>46058</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45442</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46058</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46292</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45810</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46062</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46066</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46065</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>46065</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>46294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46169</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>46294</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>46066</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>46295</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>46078</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>46296</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>46295</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45827</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45827</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>46083</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45827</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45827</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>46296</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>45980</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>46176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45477</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45833</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>46136</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46247</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45168</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34802,7 +34802,7 @@
         <v>45831</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>46050</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44526</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45982</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45843</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46301</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>46259</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46301</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44530</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46301</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>46111</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>46302</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>46302</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>46259</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46111</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>46112</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>44655</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>45621</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45610</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45439</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45414</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45085</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45826</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>46308</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45852</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45505</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44916</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>46308</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44592</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45884</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45635</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45638</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45908</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>45842</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>45054</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>45538</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45889</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>45819</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45918</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45939</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45923</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45216</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>46008</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45923</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45812</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45931</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>45923</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>46310</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45155</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45783</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>46310</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>46310</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>45937</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45702</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45940</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>46310</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>46267</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45175</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>44949</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45547</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44999</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46272</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44565</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45127</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45427</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45827</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46269</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45691</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45432</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45748</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45026</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>46272</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45825</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45197</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45146</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>46272</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>46008</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45047</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>46051</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45238</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>45566</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44975</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>45813</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45252</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45541</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44939</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45152</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45615</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45180</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45568</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45225</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45723</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45615</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46153</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>44994</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>46153</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45573</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>44830</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42746,7 +42746,7 @@
         <v>44831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>46005</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45714</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45744</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>44998</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45307</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45372</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45081</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45610</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44952</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45169</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>44999</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>44831</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45703</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45642</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45016</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45169</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>44981</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44995</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45646</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45238</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45511</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>44999</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45455</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45184</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45185</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>44526</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45149</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45713</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>44991</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45442</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45225</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45477</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45390</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45008</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45103</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45168</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45168</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45685</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45091</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>44935</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45191</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45677</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45216</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>44894</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45755</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45755</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45755</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45197</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>45194</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45532</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45690</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45218</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45248</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45019</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45019</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45736</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45099</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>45723</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>44564</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>44593</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44928</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45638</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45467</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45390</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45096</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45742</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>44896</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45170</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>44951</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>45340</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>44519</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45152</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45121</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45310</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45259</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45391</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45218</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45194</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45182</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>44994</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>44529</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44889</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>44530</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>45594</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45318</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44546</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45160</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45103</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45573</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45252</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45566</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45566</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45582</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>44966</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45016</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45723</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45719</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45439</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>44530</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45189</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50330,7 +50330,7 @@
         <v>44609</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45156</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45047</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45086</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45205</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>45681</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50768,7 +50768,7 @@
         <v>45168</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45054</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>45420</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45341</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>44740</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>45063</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51352,7 +51352,7 @@
         <v>45194</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>44547</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45616</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45216</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>44732</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>45693</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45748</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>44719</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45188</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52160,7 +52160,7 @@
         <v>45681</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45681</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>44725</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44819</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44826</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45194</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45239</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45257</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45268</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45735</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45271</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52968,7 +52968,7 @@
         <v>45378</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>45399</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53114,7 +53114,7 @@
         <v>45309</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45771</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>44818</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45302</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>44827</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45237</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>45271</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>44958</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>45054</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>45266</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>45537</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>44496</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>45693</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45693</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45610</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45455</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45328</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>44537</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>45168</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45209</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>45477</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45412</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45412</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>45524</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45691</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45559</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>44651</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45092</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45185</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>44825</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45013</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>44546</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>44600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>44575</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55611,7 +55611,7 @@
         <v>44656</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>44638</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45476</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
         <v>45106</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55903,7 +55903,7 @@
         <v>44916</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45477</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45477</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45477</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45384</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>44796</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56341,7 +56341,7 @@
         <v>45477</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45476</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45476</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>44797</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45071</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45476</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45741</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45743</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>45723</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45741</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45741</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45821</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45839</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>45845</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>45848</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45848</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45848</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45965</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>46001</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46111</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57816,7 +57816,7 @@
         <v>46273</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57889,7 +57889,7 @@
         <v>46274</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57962,7 +57962,7 @@
         <v>46274</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
